--- a/Data-raw/Raw_data_brain_bagoti_BJ.xlsx
+++ b/Data-raw/Raw_data_brain_bagoti_BJ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PATRIZIA\Desktop\These Benji\PROJECTS\Bristol\Honey pot ants project\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PATRIZIA\Desktop\These Benji\PROJECTS\Bristol\Honey pot ants project\Statistical analysis\M.bagoti-neuroanatomy-Bristol-BJ\Data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085B4094-7EB7-47EA-96B2-04BBE486A8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADE3CFE-AAB0-4A11-A381-DDE0916BBDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14250" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{81CD8C97-ABBF-4584-9E3C-0A30E205FC8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="336">
   <si>
     <t>Group</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Count</t>
   </si>
   <si>
-    <t>Volume [nm^3]</t>
-  </si>
-  <si>
     <t>Exterior</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
     <t>61180.25514</t>
   </si>
   <si>
-    <t>central_complex_body</t>
-  </si>
-  <si>
     <t>284416.249</t>
   </si>
   <si>
@@ -1045,6 +1039,9 @@
   </si>
   <si>
     <t>16477372.42</t>
+  </si>
+  <si>
+    <t>Volume</t>
   </si>
 </sst>
 </file>
@@ -1412,16 +1409,16 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -1430,10 +1427,10 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>3</v>
+        <v>335</v>
       </c>
       <c r="H1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1441,13 +1438,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1456,7 +1453,7 @@
         <v>228489852</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1464,13 +1461,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1479,7 +1476,7 @@
         <v>26337</v>
       </c>
       <c r="G3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1487,13 +1484,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1502,7 +1499,7 @@
         <v>293510</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1510,13 +1507,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1525,7 +1522,7 @@
         <v>66457</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1533,13 +1530,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -1548,7 +1545,7 @@
         <v>644024</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1556,13 +1553,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1571,7 +1568,7 @@
         <v>426962</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1579,13 +1576,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -1594,7 +1591,7 @@
         <v>7534</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1602,13 +1599,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -1617,7 +1614,7 @@
         <v>14628</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1625,13 +1622,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1640,7 +1637,7 @@
         <v>68003</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1648,13 +1645,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -1663,7 +1660,7 @@
         <v>472985</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1671,13 +1668,13 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1686,7 +1683,7 @@
         <v>378941</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1694,13 +1691,13 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E13">
         <v>11</v>
@@ -1709,7 +1706,7 @@
         <v>5040367</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1717,13 +1714,13 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1740,13 +1737,13 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1755,7 +1752,7 @@
         <v>4160</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1763,13 +1760,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1778,7 +1775,7 @@
         <v>184321</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1786,13 +1783,13 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>4</v>
@@ -1801,7 +1798,7 @@
         <v>54313</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1809,13 +1806,13 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -1824,7 +1821,7 @@
         <v>7508</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1832,13 +1829,13 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1847,7 +1844,7 @@
         <v>36760</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1855,13 +1852,13 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20">
         <v>7</v>
@@ -1870,7 +1867,7 @@
         <v>218891</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1878,13 +1875,13 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -1893,7 +1890,7 @@
         <v>361427</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1901,13 +1898,13 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E22">
         <v>9</v>
@@ -1916,7 +1913,7 @@
         <v>308988</v>
       </c>
       <c r="G22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1924,13 +1921,13 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -1939,7 +1936,7 @@
         <v>10101</v>
       </c>
       <c r="G23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1947,13 +1944,13 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>11</v>
@@ -1962,7 +1959,7 @@
         <v>3015463</v>
       </c>
       <c r="G24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1970,13 +1967,13 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E25">
         <v>12</v>
@@ -1985,7 +1982,7 @@
         <v>226693</v>
       </c>
       <c r="G25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1993,13 +1990,13 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2008,7 +2005,7 @@
         <v>184939095</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2016,13 +2013,13 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2031,7 +2028,7 @@
         <v>81801</v>
       </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2039,13 +2036,13 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -2054,7 +2051,7 @@
         <v>329377</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2062,13 +2059,13 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -2077,7 +2074,7 @@
         <v>76738</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2085,13 +2082,13 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E30">
         <v>4</v>
@@ -2100,7 +2097,7 @@
         <v>558441</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2108,13 +2105,13 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -2123,7 +2120,7 @@
         <v>4548</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2131,13 +2128,13 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -2146,7 +2143,7 @@
         <v>921807</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2154,13 +2151,13 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -2169,7 +2166,7 @@
         <v>885474</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2177,13 +2174,13 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -2192,7 +2189,7 @@
         <v>81405</v>
       </c>
       <c r="G34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2200,13 +2197,13 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E35">
         <v>9</v>
@@ -2215,7 +2212,7 @@
         <v>444014</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2223,13 +2220,13 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E36">
         <v>10</v>
@@ -2246,13 +2243,13 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -2269,13 +2266,13 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2292,13 +2289,13 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2307,7 +2304,7 @@
         <v>19675</v>
       </c>
       <c r="G39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2315,13 +2312,13 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -2330,7 +2327,7 @@
         <v>536161</v>
       </c>
       <c r="G40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2338,13 +2335,13 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -2353,7 +2350,7 @@
         <v>60633</v>
       </c>
       <c r="G41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2361,13 +2358,13 @@
         <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42">
         <v>4</v>
@@ -2376,7 +2373,7 @@
         <v>241161</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2384,13 +2381,13 @@
         <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E43">
         <v>5</v>
@@ -2399,7 +2396,7 @@
         <v>283983</v>
       </c>
       <c r="G43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2407,13 +2404,13 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E44">
         <v>6</v>
@@ -2422,7 +2419,7 @@
         <v>280868</v>
       </c>
       <c r="G44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2430,13 +2427,13 @@
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E45">
         <v>7</v>
@@ -2445,7 +2442,7 @@
         <v>5002</v>
       </c>
       <c r="G45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2453,13 +2450,13 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E46">
         <v>8</v>
@@ -2468,7 +2465,7 @@
         <v>57129</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2476,13 +2473,13 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E47">
         <v>9</v>
@@ -2491,7 +2488,7 @@
         <v>8271</v>
       </c>
       <c r="G47" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2499,13 +2496,13 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E48">
         <v>10</v>
@@ -2514,7 +2511,7 @@
         <v>411402</v>
       </c>
       <c r="G48" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2522,13 +2519,13 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E49">
         <v>11</v>
@@ -2537,7 +2534,7 @@
         <v>3704125</v>
       </c>
       <c r="G49" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2545,13 +2542,13 @@
         <v>5</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2568,13 +2565,13 @@
         <v>5</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -2583,7 +2580,7 @@
         <v>39105</v>
       </c>
       <c r="G51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2591,13 +2588,13 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E52">
         <v>2</v>
@@ -2606,7 +2603,7 @@
         <v>559222</v>
       </c>
       <c r="G52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2614,13 +2611,13 @@
         <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -2629,7 +2626,7 @@
         <v>67024</v>
       </c>
       <c r="G53" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2637,13 +2634,13 @@
         <v>5</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E54">
         <v>4</v>
@@ -2652,7 +2649,7 @@
         <v>231749</v>
       </c>
       <c r="G54" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2660,13 +2657,13 @@
         <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55">
         <v>5</v>
@@ -2675,7 +2672,7 @@
         <v>287169</v>
       </c>
       <c r="G55" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2683,13 +2680,13 @@
         <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E56">
         <v>6</v>
@@ -2698,7 +2695,7 @@
         <v>305603</v>
       </c>
       <c r="G56" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2706,13 +2703,13 @@
         <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E57">
         <v>7</v>
@@ -2721,7 +2718,7 @@
         <v>4882</v>
       </c>
       <c r="G57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2729,13 +2726,13 @@
         <v>5</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E58">
         <v>8</v>
@@ -2744,7 +2741,7 @@
         <v>66913</v>
       </c>
       <c r="G58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2752,13 +2749,13 @@
         <v>5</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E59">
         <v>9</v>
@@ -2767,7 +2764,7 @@
         <v>11132</v>
       </c>
       <c r="G59" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2775,13 +2772,13 @@
         <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E60">
         <v>10</v>
@@ -2790,7 +2787,7 @@
         <v>405853</v>
       </c>
       <c r="G60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2798,13 +2795,13 @@
         <v>5</v>
       </c>
       <c r="B61" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C61" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E61">
         <v>11</v>
@@ -2813,7 +2810,7 @@
         <v>3904656</v>
       </c>
       <c r="G61" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2821,13 +2818,13 @@
         <v>6</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2836,10 +2833,10 @@
         <v>175897690</v>
       </c>
       <c r="G62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2847,13 +2844,13 @@
         <v>6</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -2862,10 +2859,10 @@
         <v>23416</v>
       </c>
       <c r="G63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2873,13 +2870,13 @@
         <v>6</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -2888,10 +2885,10 @@
         <v>644381</v>
       </c>
       <c r="G64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2899,13 +2896,13 @@
         <v>6</v>
       </c>
       <c r="B65" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -2914,10 +2911,10 @@
         <v>78778</v>
       </c>
       <c r="G65" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2925,13 +2922,13 @@
         <v>6</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E66">
         <v>4</v>
@@ -2940,10 +2937,10 @@
         <v>260919</v>
       </c>
       <c r="G66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2951,13 +2948,13 @@
         <v>6</v>
       </c>
       <c r="B67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E67">
         <v>5</v>
@@ -2966,10 +2963,10 @@
         <v>354152</v>
       </c>
       <c r="G67" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H67" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2977,13 +2974,13 @@
         <v>6</v>
       </c>
       <c r="B68" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E68">
         <v>6</v>
@@ -2992,10 +2989,10 @@
         <v>356411</v>
       </c>
       <c r="G68" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3003,13 +3000,13 @@
         <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E69">
         <v>7</v>
@@ -3018,10 +3015,10 @@
         <v>3876</v>
       </c>
       <c r="G69" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3029,13 +3026,13 @@
         <v>6</v>
       </c>
       <c r="B70" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D70" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E70">
         <v>8</v>
@@ -3044,10 +3041,10 @@
         <v>65998</v>
       </c>
       <c r="G70" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H70" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3055,13 +3052,13 @@
         <v>6</v>
       </c>
       <c r="B71" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E71">
         <v>9</v>
@@ -3070,10 +3067,10 @@
         <v>15266</v>
       </c>
       <c r="G71" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H71" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3081,13 +3078,13 @@
         <v>6</v>
       </c>
       <c r="B72" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E72">
         <v>10</v>
@@ -3096,10 +3093,10 @@
         <v>457633</v>
       </c>
       <c r="G72" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H72" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3107,13 +3104,13 @@
         <v>6</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C73" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E73">
         <v>11</v>
@@ -3122,10 +3119,10 @@
         <v>3245128</v>
       </c>
       <c r="G73" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H73" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3133,13 +3130,13 @@
         <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3148,7 +3145,7 @@
         <v>149499792</v>
       </c>
       <c r="G74" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3156,13 +3153,13 @@
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -3171,7 +3168,7 @@
         <v>19076</v>
       </c>
       <c r="G75" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3179,13 +3176,13 @@
         <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E76">
         <v>2</v>
@@ -3194,7 +3191,7 @@
         <v>1528303</v>
       </c>
       <c r="G76" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3202,13 +3199,13 @@
         <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -3217,7 +3214,7 @@
         <v>131152</v>
       </c>
       <c r="G77" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3225,13 +3222,13 @@
         <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C78" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E78">
         <v>4</v>
@@ -3240,7 +3237,7 @@
         <v>588517</v>
       </c>
       <c r="G78" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3248,13 +3245,13 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E79">
         <v>5</v>
@@ -3263,7 +3260,7 @@
         <v>886625</v>
       </c>
       <c r="G79" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -3271,13 +3268,13 @@
         <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E80">
         <v>6</v>
@@ -3286,7 +3283,7 @@
         <v>733427</v>
       </c>
       <c r="G80" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3294,13 +3291,13 @@
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E81">
         <v>7</v>
@@ -3309,7 +3306,7 @@
         <v>11098</v>
       </c>
       <c r="G81" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3317,13 +3314,13 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E82">
         <v>8</v>
@@ -3332,7 +3329,7 @@
         <v>143989</v>
       </c>
       <c r="G82" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3340,13 +3337,13 @@
         <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E83">
         <v>9</v>
@@ -3355,7 +3352,7 @@
         <v>18477</v>
       </c>
       <c r="G83" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3363,13 +3360,13 @@
         <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E84">
         <v>10</v>
@@ -3378,7 +3375,7 @@
         <v>1059736</v>
       </c>
       <c r="G84" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3386,13 +3383,13 @@
         <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E85">
         <v>11</v>
@@ -3401,7 +3398,7 @@
         <v>8957664</v>
       </c>
       <c r="G85" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3409,13 +3406,13 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D86" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3424,7 +3421,7 @@
         <v>173721426</v>
       </c>
       <c r="G86" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3432,13 +3429,13 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C87" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -3447,7 +3444,7 @@
         <v>27343</v>
       </c>
       <c r="G87" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3455,13 +3452,13 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E88">
         <v>2</v>
@@ -3470,7 +3467,7 @@
         <v>875558</v>
       </c>
       <c r="G88" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3478,13 +3475,13 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E89">
         <v>3</v>
@@ -3493,7 +3490,7 @@
         <v>84468</v>
       </c>
       <c r="G89" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3501,13 +3498,13 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E90">
         <v>4</v>
@@ -3516,7 +3513,7 @@
         <v>387953</v>
       </c>
       <c r="G90" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3524,13 +3521,13 @@
         <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E91">
         <v>5</v>
@@ -3539,7 +3536,7 @@
         <v>512311</v>
       </c>
       <c r="G91" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3547,13 +3544,13 @@
         <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D92" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E92">
         <v>6</v>
@@ -3570,13 +3567,13 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E93">
         <v>7</v>
@@ -3585,7 +3582,7 @@
         <v>7862</v>
       </c>
       <c r="G93" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3593,13 +3590,13 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D94" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E94">
         <v>8</v>
@@ -3608,7 +3605,7 @@
         <v>78656</v>
       </c>
       <c r="G94" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3616,13 +3613,13 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E95">
         <v>9</v>
@@ -3631,7 +3628,7 @@
         <v>12327</v>
       </c>
       <c r="G95" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3639,13 +3636,13 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D96" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E96">
         <v>10</v>
@@ -3654,7 +3651,7 @@
         <v>666520</v>
       </c>
       <c r="G96" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3662,13 +3659,13 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D97" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E97">
         <v>11</v>
@@ -3677,7 +3674,7 @@
         <v>5582321</v>
       </c>
       <c r="G97" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3685,13 +3682,13 @@
         <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D98" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3700,7 +3697,7 @@
         <v>246024056</v>
       </c>
       <c r="G98" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3708,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B99" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -3723,7 +3720,7 @@
         <v>16678</v>
       </c>
       <c r="G99" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3731,13 +3728,13 @@
         <v>9</v>
       </c>
       <c r="B100" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E100">
         <v>2</v>
@@ -3746,7 +3743,7 @@
         <v>1285735</v>
       </c>
       <c r="G100" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3754,13 +3751,13 @@
         <v>9</v>
       </c>
       <c r="B101" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D101" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E101">
         <v>3</v>
@@ -3769,7 +3766,7 @@
         <v>109224</v>
       </c>
       <c r="G101" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3777,13 +3774,13 @@
         <v>9</v>
       </c>
       <c r="B102" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E102">
         <v>4</v>
@@ -3792,7 +3789,7 @@
         <v>544558</v>
       </c>
       <c r="G102" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3800,13 +3797,13 @@
         <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C103" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E103">
         <v>5</v>
@@ -3815,7 +3812,7 @@
         <v>697972</v>
       </c>
       <c r="G103" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3823,13 +3820,13 @@
         <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D104" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E104">
         <v>6</v>
@@ -3838,7 +3835,7 @@
         <v>629536</v>
       </c>
       <c r="G104" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3846,13 +3843,13 @@
         <v>9</v>
       </c>
       <c r="B105" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E105">
         <v>7</v>
@@ -3861,7 +3858,7 @@
         <v>7327</v>
       </c>
       <c r="G105" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3869,13 +3866,13 @@
         <v>9</v>
       </c>
       <c r="B106" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D106" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E106">
         <v>8</v>
@@ -3884,7 +3881,7 @@
         <v>104944</v>
       </c>
       <c r="G106" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3892,13 +3889,13 @@
         <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E107">
         <v>9</v>
@@ -3907,7 +3904,7 @@
         <v>9994</v>
       </c>
       <c r="G107" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3915,13 +3912,13 @@
         <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C108" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D108" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E108">
         <v>10</v>
@@ -3930,7 +3927,7 @@
         <v>937959</v>
       </c>
       <c r="G108" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3938,13 +3935,13 @@
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D109" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E109">
         <v>11</v>
@@ -3953,7 +3950,7 @@
         <v>7581713</v>
       </c>
       <c r="G109" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3961,13 +3958,13 @@
         <v>10</v>
       </c>
       <c r="B110" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C110" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D110" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3984,13 +3981,13 @@
         <v>10</v>
       </c>
       <c r="B111" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C111" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D111" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -3999,7 +3996,7 @@
         <v>15801</v>
       </c>
       <c r="G111" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4007,13 +4004,13 @@
         <v>10</v>
       </c>
       <c r="B112" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E112">
         <v>2</v>
@@ -4022,7 +4019,7 @@
         <v>360148</v>
       </c>
       <c r="G112" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4030,13 +4027,13 @@
         <v>10</v>
       </c>
       <c r="B113" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C113" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E113">
         <v>3</v>
@@ -4045,7 +4042,7 @@
         <v>47958</v>
       </c>
       <c r="G113" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4053,13 +4050,13 @@
         <v>10</v>
       </c>
       <c r="B114" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C114" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E114">
         <v>4</v>
@@ -4068,7 +4065,7 @@
         <v>212411</v>
       </c>
       <c r="G114" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4076,13 +4073,13 @@
         <v>10</v>
       </c>
       <c r="B115" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C115" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E115">
         <v>5</v>
@@ -4091,7 +4088,7 @@
         <v>243093</v>
       </c>
       <c r="G115" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4099,13 +4096,13 @@
         <v>10</v>
       </c>
       <c r="B116" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C116" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D116" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E116">
         <v>6</v>
@@ -4114,7 +4111,7 @@
         <v>239455</v>
       </c>
       <c r="G116" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4122,13 +4119,13 @@
         <v>10</v>
       </c>
       <c r="B117" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C117" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E117">
         <v>7</v>
@@ -4137,7 +4134,7 @@
         <v>4646</v>
       </c>
       <c r="G117" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4145,13 +4142,13 @@
         <v>10</v>
       </c>
       <c r="B118" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C118" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D118" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E118">
         <v>8</v>
@@ -4160,7 +4157,7 @@
         <v>43885</v>
       </c>
       <c r="G118" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4168,13 +4165,13 @@
         <v>10</v>
       </c>
       <c r="B119" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C119" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D119" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E119">
         <v>9</v>
@@ -4183,7 +4180,7 @@
         <v>9862</v>
       </c>
       <c r="G119" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4191,13 +4188,13 @@
         <v>10</v>
       </c>
       <c r="B120" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C120" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D120" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E120">
         <v>10</v>
@@ -4206,7 +4203,7 @@
         <v>319320</v>
       </c>
       <c r="G120" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4214,13 +4211,13 @@
         <v>10</v>
       </c>
       <c r="B121" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D121" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E121">
         <v>11</v>
@@ -4229,7 +4226,7 @@
         <v>3227735</v>
       </c>
       <c r="G121" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4237,13 +4234,13 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C122" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D122" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4260,13 +4257,13 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C123" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -4275,7 +4272,7 @@
         <v>10309</v>
       </c>
       <c r="G123" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4283,13 +4280,13 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C124" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E124">
         <v>2</v>
@@ -4298,7 +4295,7 @@
         <v>347649</v>
       </c>
       <c r="G124" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4306,13 +4303,13 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C125" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D125" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E125">
         <v>3</v>
@@ -4321,7 +4318,7 @@
         <v>35414</v>
       </c>
       <c r="G125" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4329,13 +4326,13 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C126" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D126" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E126">
         <v>4</v>
@@ -4344,7 +4341,7 @@
         <v>151117</v>
       </c>
       <c r="G126" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4352,13 +4349,13 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C127" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E127">
         <v>5</v>
@@ -4367,7 +4364,7 @@
         <v>192325</v>
       </c>
       <c r="G127" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4375,13 +4372,13 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C128" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D128" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E128">
         <v>6</v>
@@ -4390,7 +4387,7 @@
         <v>177835</v>
       </c>
       <c r="G128" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4398,13 +4395,13 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C129" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D129" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E129">
         <v>7</v>
@@ -4413,7 +4410,7 @@
         <v>3339</v>
       </c>
       <c r="G129" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4421,13 +4418,13 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C130" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D130" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E130">
         <v>8</v>
@@ -4436,7 +4433,7 @@
         <v>41215</v>
       </c>
       <c r="G130" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4444,13 +4441,13 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C131" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D131" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E131">
         <v>9</v>
@@ -4459,7 +4456,7 @@
         <v>4049</v>
       </c>
       <c r="G131" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4467,13 +4464,13 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C132" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D132" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E132">
         <v>10</v>
@@ -4482,7 +4479,7 @@
         <v>247001</v>
       </c>
       <c r="G132" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4490,13 +4487,13 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C133" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D133" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E133">
         <v>11</v>
@@ -4505,7 +4502,7 @@
         <v>2508188</v>
       </c>
       <c r="G133" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4513,13 +4510,13 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C134" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D134" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4536,13 +4533,13 @@
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C135" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D135" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -4559,13 +4556,13 @@
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C136" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E136">
         <v>2</v>
@@ -4574,7 +4571,7 @@
         <v>456131</v>
       </c>
       <c r="G136" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4582,13 +4579,13 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C137" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D137" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -4597,7 +4594,7 @@
         <v>68906</v>
       </c>
       <c r="G137" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4605,13 +4602,13 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C138" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D138" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E138">
         <v>4</v>
@@ -4620,7 +4617,7 @@
         <v>232434</v>
       </c>
       <c r="G138" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4628,13 +4625,13 @@
         <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E139">
         <v>5</v>
@@ -4643,7 +4640,7 @@
         <v>245835</v>
       </c>
       <c r="G139" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4651,13 +4648,13 @@
         <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D140" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E140">
         <v>6</v>
@@ -4666,7 +4663,7 @@
         <v>231242</v>
       </c>
       <c r="G140" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4674,13 +4671,13 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C141" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E141">
         <v>7</v>
@@ -4689,7 +4686,7 @@
         <v>3498</v>
       </c>
       <c r="G141" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4697,13 +4694,13 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C142" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D142" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E142">
         <v>8</v>
@@ -4712,7 +4709,7 @@
         <v>43495</v>
       </c>
       <c r="G142" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4720,13 +4717,13 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C143" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D143" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E143">
         <v>9</v>
@@ -4735,7 +4732,7 @@
         <v>9767</v>
       </c>
       <c r="G143" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4743,13 +4740,13 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C144" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D144" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E144">
         <v>10</v>
@@ -4758,7 +4755,7 @@
         <v>303195</v>
       </c>
       <c r="G144" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4766,13 +4763,13 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C145" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D145" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E145">
         <v>11</v>
@@ -4781,7 +4778,7 @@
         <v>2752044</v>
       </c>
       <c r="G145" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4789,13 +4786,13 @@
         <v>13</v>
       </c>
       <c r="B146" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C146" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D146" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -4804,7 +4801,7 @@
         <v>122335750</v>
       </c>
       <c r="G146" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4812,13 +4809,13 @@
         <v>13</v>
       </c>
       <c r="B147" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C147" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D147" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -4827,7 +4824,7 @@
         <v>23603</v>
       </c>
       <c r="G147" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4835,13 +4832,13 @@
         <v>13</v>
       </c>
       <c r="B148" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C148" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E148">
         <v>2</v>
@@ -4850,7 +4847,7 @@
         <v>904527</v>
       </c>
       <c r="G148" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4858,13 +4855,13 @@
         <v>13</v>
       </c>
       <c r="B149" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C149" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D149" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -4873,7 +4870,7 @@
         <v>83017</v>
       </c>
       <c r="G149" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4881,13 +4878,13 @@
         <v>13</v>
       </c>
       <c r="B150" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C150" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D150" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E150">
         <v>4</v>
@@ -4896,7 +4893,7 @@
         <v>332444</v>
       </c>
       <c r="G150" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4904,13 +4901,13 @@
         <v>13</v>
       </c>
       <c r="B151" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C151" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E151">
         <v>5</v>
@@ -4919,7 +4916,7 @@
         <v>476733</v>
       </c>
       <c r="G151" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4927,13 +4924,13 @@
         <v>13</v>
       </c>
       <c r="B152" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C152" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D152" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E152">
         <v>6</v>
@@ -4942,7 +4939,7 @@
         <v>495442</v>
       </c>
       <c r="G152" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4950,13 +4947,13 @@
         <v>13</v>
       </c>
       <c r="B153" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C153" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E153">
         <v>7</v>
@@ -4965,7 +4962,7 @@
         <v>7632</v>
       </c>
       <c r="G153" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4973,13 +4970,13 @@
         <v>13</v>
       </c>
       <c r="B154" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C154" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D154" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E154">
         <v>8</v>
@@ -4988,7 +4985,7 @@
         <v>107021</v>
       </c>
       <c r="G154" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -4996,13 +4993,13 @@
         <v>13</v>
       </c>
       <c r="B155" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C155" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D155" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E155">
         <v>9</v>
@@ -5011,7 +5008,7 @@
         <v>18150</v>
       </c>
       <c r="G155" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5019,13 +5016,13 @@
         <v>13</v>
       </c>
       <c r="B156" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C156" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D156" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E156">
         <v>10</v>
@@ -5034,7 +5031,7 @@
         <v>741654</v>
       </c>
       <c r="G156" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5042,13 +5039,13 @@
         <v>13</v>
       </c>
       <c r="B157" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C157" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D157" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E157">
         <v>11</v>
@@ -5057,7 +5054,7 @@
         <v>6594603</v>
       </c>
       <c r="G157" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5065,13 +5062,13 @@
         <v>14</v>
       </c>
       <c r="B158" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C158" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D158" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5080,7 +5077,7 @@
         <v>175551971</v>
       </c>
       <c r="G158" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5088,13 +5085,13 @@
         <v>14</v>
       </c>
       <c r="B159" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C159" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D159" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -5103,7 +5100,7 @@
         <v>24432</v>
       </c>
       <c r="G159" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5111,13 +5108,13 @@
         <v>14</v>
       </c>
       <c r="B160" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C160" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -5126,7 +5123,7 @@
         <v>972178</v>
       </c>
       <c r="G160" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5134,13 +5131,13 @@
         <v>14</v>
       </c>
       <c r="B161" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C161" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D161" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E161">
         <v>3</v>
@@ -5149,7 +5146,7 @@
         <v>97227</v>
       </c>
       <c r="G161" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5157,13 +5154,13 @@
         <v>14</v>
       </c>
       <c r="B162" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C162" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D162" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E162">
         <v>4</v>
@@ -5172,7 +5169,7 @@
         <v>403860</v>
       </c>
       <c r="G162" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5180,13 +5177,13 @@
         <v>14</v>
       </c>
       <c r="B163" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C163" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D163" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E163">
         <v>5</v>
@@ -5195,7 +5192,7 @@
         <v>535532</v>
       </c>
       <c r="G163" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5203,13 +5200,13 @@
         <v>14</v>
       </c>
       <c r="B164" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C164" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D164" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E164">
         <v>6</v>
@@ -5218,7 +5215,7 @@
         <v>496351</v>
       </c>
       <c r="G164" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5226,13 +5223,13 @@
         <v>14</v>
       </c>
       <c r="B165" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C165" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D165" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E165">
         <v>7</v>
@@ -5241,7 +5238,7 @@
         <v>9242</v>
       </c>
       <c r="G165" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5249,13 +5246,13 @@
         <v>14</v>
       </c>
       <c r="B166" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C166" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D166" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E166">
         <v>8</v>
@@ -5264,7 +5261,7 @@
         <v>113350</v>
       </c>
       <c r="G166" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5272,13 +5269,13 @@
         <v>14</v>
       </c>
       <c r="B167" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C167" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D167" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E167">
         <v>9</v>
@@ -5287,7 +5284,7 @@
         <v>19823</v>
       </c>
       <c r="G167" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5295,13 +5292,13 @@
         <v>14</v>
       </c>
       <c r="B168" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C168" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D168" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E168">
         <v>10</v>
@@ -5310,7 +5307,7 @@
         <v>915193</v>
       </c>
       <c r="G168" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5318,13 +5315,13 @@
         <v>14</v>
       </c>
       <c r="B169" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C169" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D169" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E169">
         <v>11</v>
@@ -5333,7 +5330,7 @@
         <v>7507369</v>
       </c>
       <c r="G169" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5341,13 +5338,13 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C170" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D170" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5356,7 +5353,7 @@
         <v>144469517</v>
       </c>
       <c r="G170" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5364,13 +5361,13 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C171" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D171" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E171">
         <v>1</v>
@@ -5379,7 +5376,7 @@
         <v>19703</v>
       </c>
       <c r="G171" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5387,13 +5384,13 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C172" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D172" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -5402,7 +5399,7 @@
         <v>1365731</v>
       </c>
       <c r="G172" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5410,13 +5407,13 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C173" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D173" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E173">
         <v>3</v>
@@ -5425,7 +5422,7 @@
         <v>98088</v>
       </c>
       <c r="G173" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5433,13 +5430,13 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C174" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D174" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E174">
         <v>4</v>
@@ -5448,7 +5445,7 @@
         <v>468258</v>
       </c>
       <c r="G174" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5456,13 +5453,13 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C175" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D175" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E175">
         <v>5</v>
@@ -5471,7 +5468,7 @@
         <v>751791</v>
       </c>
       <c r="G175" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5479,13 +5476,13 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C176" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D176" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E176">
         <v>6</v>
@@ -5494,7 +5491,7 @@
         <v>729687</v>
       </c>
       <c r="G176" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5502,13 +5499,13 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C177" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E177">
         <v>7</v>
@@ -5517,7 +5514,7 @@
         <v>13079</v>
       </c>
       <c r="G177" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5525,13 +5522,13 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C178" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D178" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E178">
         <v>8</v>
@@ -5540,7 +5537,7 @@
         <v>107533</v>
       </c>
       <c r="G178" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5548,13 +5545,13 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C179" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D179" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E179">
         <v>9</v>
@@ -5563,7 +5560,7 @@
         <v>17280</v>
       </c>
       <c r="G179" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5571,13 +5568,13 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C180" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D180" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E180">
         <v>10</v>
@@ -5586,7 +5583,7 @@
         <v>938465</v>
       </c>
       <c r="G180" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5594,13 +5591,13 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C181" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D181" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E181">
         <v>11</v>
@@ -5609,7 +5606,7 @@
         <v>8307268</v>
       </c>
       <c r="G181" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5617,13 +5614,13 @@
         <v>16</v>
       </c>
       <c r="B182" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C182" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D182" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -5632,7 +5629,7 @@
         <v>192429826</v>
       </c>
       <c r="G182" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5640,13 +5637,13 @@
         <v>16</v>
       </c>
       <c r="B183" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C183" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D183" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -5655,7 +5652,7 @@
         <v>16822</v>
       </c>
       <c r="G183" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5663,13 +5660,13 @@
         <v>16</v>
       </c>
       <c r="B184" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C184" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D184" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E184">
         <v>2</v>
@@ -5678,7 +5675,7 @@
         <v>698570</v>
       </c>
       <c r="G184" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5686,13 +5683,13 @@
         <v>16</v>
       </c>
       <c r="B185" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C185" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D185" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E185">
         <v>3</v>
@@ -5701,7 +5698,7 @@
         <v>78535</v>
       </c>
       <c r="G185" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5709,13 +5706,13 @@
         <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C186" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D186" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E186">
         <v>4</v>
@@ -5724,7 +5721,7 @@
         <v>248682</v>
       </c>
       <c r="G186" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5732,13 +5729,13 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D187" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E187">
         <v>5</v>
@@ -5747,7 +5744,7 @@
         <v>356647</v>
       </c>
       <c r="G187" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5755,13 +5752,13 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C188" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D188" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E188">
         <v>6</v>
@@ -5770,7 +5767,7 @@
         <v>330347</v>
       </c>
       <c r="G188" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5778,13 +5775,13 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C189" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D189" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E189">
         <v>7</v>
@@ -5793,7 +5790,7 @@
         <v>5779</v>
       </c>
       <c r="G189" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5801,13 +5798,13 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C190" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D190" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E190">
         <v>8</v>
@@ -5816,7 +5813,7 @@
         <v>67952</v>
       </c>
       <c r="G190" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5824,13 +5821,13 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C191" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D191" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E191">
         <v>9</v>
@@ -5839,7 +5836,7 @@
         <v>10526</v>
       </c>
       <c r="G191" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5847,13 +5844,13 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C192" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D192" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E192">
         <v>10</v>
@@ -5862,7 +5859,7 @@
         <v>450735</v>
       </c>
       <c r="G192" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5870,13 +5867,13 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C193" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D193" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E193">
         <v>11</v>
@@ -5885,7 +5882,7 @@
         <v>4535019</v>
       </c>
       <c r="G193" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5893,13 +5890,13 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C194" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D194" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -5916,13 +5913,13 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C195" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D195" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -5931,7 +5928,7 @@
         <v>22522</v>
       </c>
       <c r="G195" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5939,13 +5936,13 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C196" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D196" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -5954,7 +5951,7 @@
         <v>777162</v>
       </c>
       <c r="G196" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5962,13 +5959,13 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C197" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D197" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E197">
         <v>3</v>
@@ -5977,7 +5974,7 @@
         <v>62740</v>
       </c>
       <c r="G197" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -5985,13 +5982,13 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C198" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D198" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E198">
         <v>4</v>
@@ -6000,7 +5997,7 @@
         <v>270323</v>
       </c>
       <c r="G198" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6008,13 +6005,13 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C199" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D199" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E199">
         <v>5</v>
@@ -6023,7 +6020,7 @@
         <v>492868</v>
       </c>
       <c r="G199" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6031,13 +6028,13 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C200" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D200" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E200">
         <v>6</v>
@@ -6046,7 +6043,7 @@
         <v>492005</v>
       </c>
       <c r="G200" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6054,13 +6051,13 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C201" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E201">
         <v>7</v>
@@ -6069,7 +6066,7 @@
         <v>5327</v>
       </c>
       <c r="G201" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6077,13 +6074,13 @@
         <v>17</v>
       </c>
       <c r="B202" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D202" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E202">
         <v>8</v>
@@ -6092,7 +6089,7 @@
         <v>74257</v>
       </c>
       <c r="G202" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6100,13 +6097,13 @@
         <v>17</v>
       </c>
       <c r="B203" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C203" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D203" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E203">
         <v>9</v>
@@ -6115,7 +6112,7 @@
         <v>9591</v>
       </c>
       <c r="G203" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6123,13 +6120,13 @@
         <v>17</v>
       </c>
       <c r="B204" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C204" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D204" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E204">
         <v>10</v>
@@ -6138,7 +6135,7 @@
         <v>628008</v>
       </c>
       <c r="G204" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6146,13 +6143,13 @@
         <v>17</v>
       </c>
       <c r="B205" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C205" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D205" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E205">
         <v>11</v>
@@ -6161,7 +6158,7 @@
         <v>4505769</v>
       </c>
       <c r="G205" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6169,13 +6166,13 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C206" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D206" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6192,13 +6189,13 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C207" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D207" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E207">
         <v>1</v>
@@ -6207,7 +6204,7 @@
         <v>14499</v>
       </c>
       <c r="G207" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6215,13 +6212,13 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C208" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D208" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E208">
         <v>2</v>
@@ -6230,7 +6227,7 @@
         <v>502613</v>
       </c>
       <c r="G208" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6238,13 +6235,13 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C209" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D209" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E209">
         <v>3</v>
@@ -6253,7 +6250,7 @@
         <v>49906</v>
       </c>
       <c r="G209" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6261,13 +6258,13 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C210" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D210" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E210">
         <v>4</v>
@@ -6276,7 +6273,7 @@
         <v>207132</v>
       </c>
       <c r="G210" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6284,13 +6281,13 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D211" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E211">
         <v>5</v>
@@ -6299,7 +6296,7 @@
         <v>305138</v>
       </c>
       <c r="G211" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6307,13 +6304,13 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C212" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D212" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E212">
         <v>6</v>
@@ -6322,7 +6319,7 @@
         <v>299551</v>
       </c>
       <c r="G212" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6330,13 +6327,13 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C213" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D213" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E213">
         <v>7</v>
@@ -6345,7 +6342,7 @@
         <v>4290</v>
       </c>
       <c r="G213" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6353,13 +6350,13 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C214" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D214" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E214">
         <v>8</v>
@@ -6368,7 +6365,7 @@
         <v>57142</v>
       </c>
       <c r="G214" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6376,13 +6373,13 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C215" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D215" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E215">
         <v>9</v>
@@ -6391,7 +6388,7 @@
         <v>12054</v>
       </c>
       <c r="G215" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6399,13 +6396,13 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C216" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D216" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E216">
         <v>10</v>
@@ -6414,7 +6411,7 @@
         <v>328351</v>
       </c>
       <c r="G216" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6422,13 +6419,13 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C217" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D217" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E217">
         <v>11</v>
@@ -6437,7 +6434,7 @@
         <v>3648766</v>
       </c>
       <c r="G217" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6445,13 +6442,13 @@
         <v>19</v>
       </c>
       <c r="B218" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C218" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D218" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -6460,7 +6457,7 @@
         <v>210511962</v>
       </c>
       <c r="G218" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6468,13 +6465,13 @@
         <v>19</v>
       </c>
       <c r="B219" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C219" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D219" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E219">
         <v>1</v>
@@ -6483,7 +6480,7 @@
         <v>24757</v>
       </c>
       <c r="G219" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6491,13 +6488,13 @@
         <v>19</v>
       </c>
       <c r="B220" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C220" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D220" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E220">
         <v>2</v>
@@ -6506,7 +6503,7 @@
         <v>1327192</v>
       </c>
       <c r="G220" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6514,13 +6511,13 @@
         <v>19</v>
       </c>
       <c r="B221" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C221" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D221" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E221">
         <v>3</v>
@@ -6529,7 +6526,7 @@
         <v>91437</v>
       </c>
       <c r="G221" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6537,13 +6534,13 @@
         <v>19</v>
       </c>
       <c r="B222" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C222" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D222" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E222">
         <v>4</v>
@@ -6552,7 +6549,7 @@
         <v>476248</v>
       </c>
       <c r="G222" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6560,13 +6557,13 @@
         <v>19</v>
       </c>
       <c r="B223" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C223" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D223" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E223">
         <v>5</v>
@@ -6575,7 +6572,7 @@
         <v>865773</v>
       </c>
       <c r="G223" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6583,13 +6580,13 @@
         <v>19</v>
       </c>
       <c r="B224" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C224" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D224" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E224">
         <v>6</v>
@@ -6598,7 +6595,7 @@
         <v>808506</v>
       </c>
       <c r="G224" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6606,13 +6603,13 @@
         <v>19</v>
       </c>
       <c r="B225" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C225" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D225" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E225">
         <v>7</v>
@@ -6621,7 +6618,7 @@
         <v>8257</v>
       </c>
       <c r="G225" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6629,13 +6626,13 @@
         <v>19</v>
       </c>
       <c r="B226" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C226" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D226" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E226">
         <v>8</v>
@@ -6644,7 +6641,7 @@
         <v>121478</v>
       </c>
       <c r="G226" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6652,13 +6649,13 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C227" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D227" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E227">
         <v>9</v>
@@ -6667,7 +6664,7 @@
         <v>18427</v>
       </c>
       <c r="G227" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6675,13 +6672,13 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C228" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D228" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E228">
         <v>10</v>
@@ -6690,7 +6687,7 @@
         <v>960290</v>
       </c>
       <c r="G228" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6698,13 +6695,13 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C229" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D229" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E229">
         <v>11</v>
@@ -6713,7 +6710,7 @@
         <v>8132361</v>
       </c>
       <c r="G229" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6721,13 +6718,13 @@
         <v>20</v>
       </c>
       <c r="B230" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C230" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D230" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -6744,13 +6741,13 @@
         <v>20</v>
       </c>
       <c r="B231" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C231" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D231" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E231">
         <v>1</v>
@@ -6759,7 +6756,7 @@
         <v>13542</v>
       </c>
       <c r="G231" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6767,13 +6764,13 @@
         <v>20</v>
       </c>
       <c r="B232" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C232" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D232" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E232">
         <v>2</v>
@@ -6782,7 +6779,7 @@
         <v>478522</v>
       </c>
       <c r="G232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6790,13 +6787,13 @@
         <v>20</v>
       </c>
       <c r="B233" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C233" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D233" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E233">
         <v>3</v>
@@ -6805,7 +6802,7 @@
         <v>52997</v>
       </c>
       <c r="G233" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6813,13 +6810,13 @@
         <v>20</v>
       </c>
       <c r="B234" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C234" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D234" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E234">
         <v>4</v>
@@ -6828,7 +6825,7 @@
         <v>188984</v>
       </c>
       <c r="G234" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6836,13 +6833,13 @@
         <v>20</v>
       </c>
       <c r="B235" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C235" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D235" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E235">
         <v>5</v>
@@ -6851,7 +6848,7 @@
         <v>245859</v>
       </c>
       <c r="G235" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6859,13 +6856,13 @@
         <v>20</v>
       </c>
       <c r="B236" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C236" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D236" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E236">
         <v>6</v>
@@ -6874,7 +6871,7 @@
         <v>250251</v>
       </c>
       <c r="G236" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6882,13 +6879,13 @@
         <v>20</v>
       </c>
       <c r="B237" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C237" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E237">
         <v>7</v>
@@ -6897,7 +6894,7 @@
         <v>3730</v>
       </c>
       <c r="G237" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6905,13 +6902,13 @@
         <v>20</v>
       </c>
       <c r="B238" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C238" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D238" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E238">
         <v>8</v>
@@ -6920,7 +6917,7 @@
         <v>50526</v>
       </c>
       <c r="G238" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6928,13 +6925,13 @@
         <v>20</v>
       </c>
       <c r="B239" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C239" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D239" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E239">
         <v>9</v>
@@ -6943,7 +6940,7 @@
         <v>9718</v>
       </c>
       <c r="G239" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6951,13 +6948,13 @@
         <v>20</v>
       </c>
       <c r="B240" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C240" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D240" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E240">
         <v>10</v>
@@ -6966,7 +6963,7 @@
         <v>311586</v>
       </c>
       <c r="G240" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6974,13 +6971,13 @@
         <v>20</v>
       </c>
       <c r="B241" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C241" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D241" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E241">
         <v>11</v>
@@ -6989,7 +6986,7 @@
         <v>3434569</v>
       </c>
       <c r="G241" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6997,13 +6994,13 @@
         <v>21</v>
       </c>
       <c r="B242" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C242" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D242" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -7012,7 +7009,7 @@
         <v>152949381</v>
       </c>
       <c r="G242" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7020,13 +7017,13 @@
         <v>21</v>
       </c>
       <c r="B243" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C243" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D243" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E243">
         <v>1</v>
@@ -7035,7 +7032,7 @@
         <v>9471</v>
       </c>
       <c r="G243" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7043,13 +7040,13 @@
         <v>21</v>
       </c>
       <c r="B244" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C244" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D244" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E244">
         <v>2</v>
@@ -7058,7 +7055,7 @@
         <v>572786</v>
       </c>
       <c r="G244" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7066,13 +7063,13 @@
         <v>21</v>
       </c>
       <c r="B245" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C245" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D245" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E245">
         <v>3</v>
@@ -7081,7 +7078,7 @@
         <v>53150</v>
       </c>
       <c r="G245" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7089,13 +7086,13 @@
         <v>21</v>
       </c>
       <c r="B246" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C246" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D246" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E246">
         <v>4</v>
@@ -7104,7 +7101,7 @@
         <v>203416</v>
       </c>
       <c r="G246" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7112,13 +7109,13 @@
         <v>21</v>
       </c>
       <c r="B247" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C247" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D247" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E247">
         <v>5</v>
@@ -7127,7 +7124,7 @@
         <v>283656</v>
       </c>
       <c r="G247" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7135,13 +7132,13 @@
         <v>21</v>
       </c>
       <c r="B248" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C248" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D248" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E248">
         <v>6</v>
@@ -7150,7 +7147,7 @@
         <v>282372</v>
       </c>
       <c r="G248" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7158,13 +7155,13 @@
         <v>21</v>
       </c>
       <c r="B249" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C249" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D249" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E249">
         <v>7</v>
@@ -7173,7 +7170,7 @@
         <v>3730</v>
       </c>
       <c r="G249" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7181,13 +7178,13 @@
         <v>21</v>
       </c>
       <c r="B250" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C250" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D250" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E250">
         <v>8</v>
@@ -7196,7 +7193,7 @@
         <v>54806</v>
       </c>
       <c r="G250" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7204,13 +7201,13 @@
         <v>21</v>
       </c>
       <c r="B251" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C251" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D251" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E251">
         <v>9</v>
@@ -7219,7 +7216,7 @@
         <v>9219</v>
       </c>
       <c r="G251" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7227,13 +7224,13 @@
         <v>21</v>
       </c>
       <c r="B252" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C252" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D252" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E252">
         <v>10</v>
@@ -7242,7 +7239,7 @@
         <v>384067</v>
       </c>
       <c r="G252" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7250,13 +7247,13 @@
         <v>21</v>
       </c>
       <c r="B253" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C253" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D253" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E253">
         <v>11</v>
@@ -7265,7 +7262,7 @@
         <v>3528922</v>
       </c>
       <c r="G253" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7273,13 +7270,13 @@
         <v>22</v>
       </c>
       <c r="B254" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C254" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D254" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -7288,7 +7285,7 @@
         <v>139806995</v>
       </c>
       <c r="G254" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7296,13 +7293,13 @@
         <v>22</v>
       </c>
       <c r="B255" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C255" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D255" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E255">
         <v>1</v>
@@ -7311,7 +7308,7 @@
         <v>14627</v>
       </c>
       <c r="G255" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7319,13 +7316,13 @@
         <v>22</v>
       </c>
       <c r="B256" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C256" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D256" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E256">
         <v>2</v>
@@ -7334,7 +7331,7 @@
         <v>797574</v>
       </c>
       <c r="G256" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7342,13 +7339,13 @@
         <v>22</v>
       </c>
       <c r="B257" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C257" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D257" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E257">
         <v>3</v>
@@ -7357,7 +7354,7 @@
         <v>85840</v>
       </c>
       <c r="G257" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7365,13 +7362,13 @@
         <v>22</v>
       </c>
       <c r="B258" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C258" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D258" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E258">
         <v>4</v>
@@ -7380,7 +7377,7 @@
         <v>358265</v>
       </c>
       <c r="G258" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7388,13 +7385,13 @@
         <v>22</v>
       </c>
       <c r="B259" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C259" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D259" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E259">
         <v>5</v>
@@ -7403,7 +7400,7 @@
         <v>433196</v>
       </c>
       <c r="G259" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7411,13 +7408,13 @@
         <v>22</v>
       </c>
       <c r="B260" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C260" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D260" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E260">
         <v>6</v>
@@ -7426,7 +7423,7 @@
         <v>427574</v>
       </c>
       <c r="G260" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7434,13 +7431,13 @@
         <v>22</v>
       </c>
       <c r="B261" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C261" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D261" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E261">
         <v>7</v>
@@ -7449,7 +7446,7 @@
         <v>6471</v>
       </c>
       <c r="G261" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7457,13 +7454,13 @@
         <v>22</v>
       </c>
       <c r="B262" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C262" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D262" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E262">
         <v>8</v>
@@ -7472,7 +7469,7 @@
         <v>81565</v>
       </c>
       <c r="G262" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7480,13 +7477,13 @@
         <v>22</v>
       </c>
       <c r="B263" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C263" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D263" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E263">
         <v>9</v>
@@ -7495,7 +7492,7 @@
         <v>11341</v>
       </c>
       <c r="G263" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7503,13 +7500,13 @@
         <v>22</v>
       </c>
       <c r="B264" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C264" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D264" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E264">
         <v>10</v>
@@ -7518,7 +7515,7 @@
         <v>499022</v>
       </c>
       <c r="G264" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7526,13 +7523,13 @@
         <v>22</v>
       </c>
       <c r="B265" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C265" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D265" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E265">
         <v>11</v>
@@ -7541,7 +7538,7 @@
         <v>5326746</v>
       </c>
       <c r="G265" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7549,13 +7546,13 @@
         <v>23</v>
       </c>
       <c r="B266" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C266" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D266" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -7564,7 +7561,7 @@
         <v>149565515</v>
       </c>
       <c r="G266" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7572,13 +7569,13 @@
         <v>23</v>
       </c>
       <c r="B267" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C267" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D267" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E267">
         <v>1</v>
@@ -7587,7 +7584,7 @@
         <v>27174</v>
       </c>
       <c r="G267" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7595,13 +7592,13 @@
         <v>23</v>
       </c>
       <c r="B268" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C268" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D268" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E268">
         <v>2</v>
@@ -7610,7 +7607,7 @@
         <v>543385</v>
       </c>
       <c r="G268" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7618,13 +7615,13 @@
         <v>23</v>
       </c>
       <c r="B269" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C269" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D269" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E269">
         <v>3</v>
@@ -7633,7 +7630,7 @@
         <v>70945</v>
       </c>
       <c r="G269" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7641,13 +7638,13 @@
         <v>23</v>
       </c>
       <c r="B270" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C270" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D270" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E270">
         <v>4</v>
@@ -7656,7 +7653,7 @@
         <v>250374</v>
       </c>
       <c r="G270" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7664,13 +7661,13 @@
         <v>23</v>
       </c>
       <c r="B271" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C271" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D271" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E271">
         <v>5</v>
@@ -7679,7 +7676,7 @@
         <v>269835</v>
       </c>
       <c r="G271" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7687,13 +7684,13 @@
         <v>23</v>
       </c>
       <c r="B272" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C272" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D272" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E272">
         <v>6</v>
@@ -7702,7 +7699,7 @@
         <v>300036</v>
       </c>
       <c r="G272" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7710,13 +7707,13 @@
         <v>23</v>
       </c>
       <c r="B273" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C273" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D273" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E273">
         <v>7</v>
@@ -7725,7 +7722,7 @@
         <v>5486</v>
       </c>
       <c r="G273" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7733,13 +7730,13 @@
         <v>23</v>
       </c>
       <c r="B274" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C274" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D274" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E274">
         <v>8</v>
@@ -7748,7 +7745,7 @@
         <v>65028</v>
       </c>
       <c r="G274" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7756,13 +7753,13 @@
         <v>23</v>
       </c>
       <c r="B275" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C275" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D275" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E275">
         <v>9</v>
@@ -7771,7 +7768,7 @@
         <v>12119</v>
       </c>
       <c r="G275" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7779,13 +7776,13 @@
         <v>23</v>
       </c>
       <c r="B276" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C276" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D276" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E276">
         <v>10</v>
@@ -7794,7 +7791,7 @@
         <v>444672</v>
       </c>
       <c r="G276" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7802,13 +7799,13 @@
         <v>23</v>
       </c>
       <c r="B277" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C277" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D277" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E277">
         <v>11</v>
@@ -7817,7 +7814,7 @@
         <v>4409241</v>
       </c>
       <c r="G277" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7825,13 +7822,13 @@
         <v>24</v>
       </c>
       <c r="B278" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C278" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D278" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -7840,7 +7837,7 @@
         <v>162045018</v>
       </c>
       <c r="G278" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7848,13 +7845,13 @@
         <v>24</v>
       </c>
       <c r="B279" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C279" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D279" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E279">
         <v>1</v>
@@ -7863,7 +7860,7 @@
         <v>18875</v>
       </c>
       <c r="G279" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7871,13 +7868,13 @@
         <v>24</v>
       </c>
       <c r="B280" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C280" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D280" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E280">
         <v>2</v>
@@ -7886,7 +7883,7 @@
         <v>630934</v>
       </c>
       <c r="G280" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7894,13 +7891,13 @@
         <v>24</v>
       </c>
       <c r="B281" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C281" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D281" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E281">
         <v>3</v>
@@ -7909,7 +7906,7 @@
         <v>76536</v>
       </c>
       <c r="G281" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7917,13 +7914,13 @@
         <v>24</v>
       </c>
       <c r="B282" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C282" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D282" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E282">
         <v>4</v>
@@ -7932,7 +7929,7 @@
         <v>284649</v>
       </c>
       <c r="G282" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7940,13 +7937,13 @@
         <v>24</v>
       </c>
       <c r="B283" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C283" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D283" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E283">
         <v>5</v>
@@ -7955,7 +7952,7 @@
         <v>366719</v>
       </c>
       <c r="G283" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7963,13 +7960,13 @@
         <v>24</v>
       </c>
       <c r="B284" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C284" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D284" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E284">
         <v>6</v>
@@ -7978,7 +7975,7 @@
         <v>361232</v>
       </c>
       <c r="G284" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7986,13 +7983,13 @@
         <v>24</v>
       </c>
       <c r="B285" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C285" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D285" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E285">
         <v>7</v>
@@ -8001,7 +7998,7 @@
         <v>4422</v>
       </c>
       <c r="G285" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8009,13 +8006,13 @@
         <v>24</v>
       </c>
       <c r="B286" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C286" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D286" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E286">
         <v>8</v>
@@ -8024,7 +8021,7 @@
         <v>79208</v>
       </c>
       <c r="G286" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8032,13 +8029,13 @@
         <v>24</v>
       </c>
       <c r="B287" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C287" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D287" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E287">
         <v>9</v>
@@ -8047,7 +8044,7 @@
         <v>17253</v>
       </c>
       <c r="G287" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8055,13 +8052,13 @@
         <v>24</v>
       </c>
       <c r="B288" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C288" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D288" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E288">
         <v>10</v>
@@ -8070,7 +8067,7 @@
         <v>490521</v>
       </c>
       <c r="G288" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8078,13 +8075,13 @@
         <v>24</v>
       </c>
       <c r="B289" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C289" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D289" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E289">
         <v>11</v>
@@ -8093,7 +8090,7 @@
         <v>4445369</v>
       </c>
       <c r="G289" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8101,13 +8098,13 @@
         <v>25</v>
       </c>
       <c r="B290" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C290" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D290" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -8116,7 +8113,7 @@
         <v>159451424</v>
       </c>
       <c r="G290" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8124,13 +8121,13 @@
         <v>25</v>
       </c>
       <c r="B291" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C291" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D291" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E291">
         <v>1</v>
@@ -8139,7 +8136,7 @@
         <v>20919</v>
       </c>
       <c r="G291" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8147,13 +8144,13 @@
         <v>25</v>
       </c>
       <c r="B292" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C292" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D292" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E292">
         <v>2</v>
@@ -8162,7 +8159,7 @@
         <v>814735</v>
       </c>
       <c r="G292" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8170,13 +8167,13 @@
         <v>25</v>
       </c>
       <c r="B293" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C293" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D293" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E293">
         <v>3</v>
@@ -8185,7 +8182,7 @@
         <v>71607</v>
       </c>
       <c r="G293" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8193,13 +8190,13 @@
         <v>25</v>
       </c>
       <c r="B294" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C294" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D294" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E294">
         <v>4</v>
@@ -8208,7 +8205,7 @@
         <v>319355</v>
       </c>
       <c r="G294" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8216,13 +8213,13 @@
         <v>25</v>
       </c>
       <c r="B295" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C295" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D295" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E295">
         <v>5</v>
@@ -8231,7 +8228,7 @@
         <v>438042</v>
       </c>
       <c r="G295" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8239,13 +8236,13 @@
         <v>25</v>
       </c>
       <c r="B296" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C296" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D296" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E296">
         <v>6</v>
@@ -8254,7 +8251,7 @@
         <v>435278</v>
       </c>
       <c r="G296" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8262,13 +8259,13 @@
         <v>25</v>
       </c>
       <c r="B297" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C297" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D297" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E297">
         <v>7</v>
@@ -8277,7 +8274,7 @@
         <v>7692</v>
       </c>
       <c r="G297" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8285,13 +8282,13 @@
         <v>25</v>
       </c>
       <c r="B298" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C298" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D298" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E298">
         <v>8</v>
@@ -8300,7 +8297,7 @@
         <v>89499</v>
       </c>
       <c r="G298" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8308,13 +8305,13 @@
         <v>25</v>
       </c>
       <c r="B299" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C299" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D299" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E299">
         <v>9</v>
@@ -8323,7 +8320,7 @@
         <v>9949</v>
       </c>
       <c r="G299" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8331,13 +8328,13 @@
         <v>25</v>
       </c>
       <c r="B300" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C300" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D300" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E300">
         <v>10</v>
@@ -8346,7 +8343,7 @@
         <v>661412</v>
       </c>
       <c r="G300" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8354,13 +8351,13 @@
         <v>25</v>
       </c>
       <c r="B301" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C301" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D301" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E301">
         <v>11</v>
@@ -8369,7 +8366,7 @@
         <v>5452248</v>
       </c>
       <c r="G301" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
